--- a/outputs/萌开了家居_运费价格表_普通快递-顺丰-安能.xlsx
+++ b/outputs/萌开了家居_运费价格表_普通快递-顺丰-安能.xlsx
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>1.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K22" s="11">
         <f>G22</f>
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="L22" s="9">
         <f>C22+(20-1)*D22</f>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="N22" s="11">
         <f>G22+(20-15)*H22</f>
-        <v>117.5</v>
+        <v>45.5</v>
       </c>
       <c r="O22" s="7" t="str">
         <f>IF(AND(I22&lt;=J22,I22&lt;=K22),"普通快递",IF(J22&lt;=K22,"顺丰快递","安能物流"))</f>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P22" s="7" t="str">
         <f>IF(AND(L22&lt;=M22,L22&lt;=N22),"普通快递",IF(M22&lt;=N22,"顺丰快递","安能物流"))</f>
-        <v>普通快递</v>
+        <v>安能物流</v>
       </c>
     </row>
     <row r="23">
@@ -2373,10 +2373,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>33</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="J32" s="10">
         <f>E32+(5-1)*F32</f>
-        <v>47.0</v>
+        <v>42.0</v>
       </c>
       <c r="K32" s="11">
         <f>G32</f>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="M32" s="10">
         <f>E32+(20-1)*F32</f>
-        <v>152.0</v>
+        <v>132.0</v>
       </c>
       <c r="N32" s="11">
         <f>G32+(20-15)*H32</f>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D35" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F35" s="14" t="n">
         <v>5</v>
@@ -2568,11 +2568,11 @@
       </c>
       <c r="I35" s="14">
         <f>C35+(5-1)*D35</f>
-        <v>38.0</v>
+        <v>32.0</v>
       </c>
       <c r="J35" s="14">
         <f>E35+(5-1)*F35</f>
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="K35" s="14">
         <f>G35</f>
@@ -2580,11 +2580,11 @@
       </c>
       <c r="L35" s="14">
         <f>C35+(20-1)*D35</f>
-        <v>113.0</v>
+        <v>107.0</v>
       </c>
       <c r="M35" s="14">
         <f>E35+(20-1)*F35</f>
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="N35" s="14">
         <f>G35+(20-15)*H35</f>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="O35" s="12" t="str">
         <f>IF(AND(I35&lt;=J35,I35&lt;=K35),"普通快递",IF(J35&lt;=K35,"顺丰快递","安能物流"))</f>
-        <v>顺丰快递</v>
+        <v>普通快递</v>
       </c>
       <c r="P35" s="12" t="str">
         <f>IF(AND(L35&lt;=M35,L35&lt;=N35),"普通快递",IF(M35&lt;=N35,"顺丰快递","安能物流"))</f>
@@ -2923,36 +2923,36 @@
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>⚠ 需核对 1</t>
+          <t>✅ 已修正（2026-10-29）</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>安能山西为 ¥110 首重（¥1.5 续重），而周边陕西 ¥38、河南 ¥33、河北 ¥33，山西明显异常，疑为录入笔误。</t>
+          <t>安能山西原录 ¥110，店主确认应为 ¥38（与福建、广东同为 38 档），已改 constants.ts；江苏顺丰由 ¥19/¥7 改为 ¥18/¥6（同上海、浙江）；本表已是修正后的价格。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>⚠ 需核对 2</t>
+          <t>⚠ 仍需核对 1</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>江苏顺丰 ¥19/¥7，而同区域的上海、浙江、安徽都是 ¥18 起；山西顺丰 ¥19/¥6，同片陕西 ¥18/¥5，两处都偏高。</t>
+          <t>山西顺丰 ¥19/¥6，同片陕西 ¥18/¥5，偏高 1 元，至今未确认是否笔误。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>⚠ 需核对 3</t>
+          <t>✅ 兜底价已修正（2026-10-29）</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>省份在表里查不到时，系统兜底用「普通 ¥18/¥5、顺丰 ¥15/¥5、安能 ¥50/¥3」——顺丰兜底价低于绝大多数真实省份（普遍 ¥18 起），一旦出现未匹配省份会少收运费。</t>
+          <t>省份在表里查不到时，系统兜底用「普通 ¥12/¥5、顺丰 ¥18/¥5、安能 ¥50/¥3」——顺丰兜底首重原为 ¥15、普通兜底首重原为 ¥18（均按店主 10-29 确认调整），现在不会再因未匹配省份而明显多收/少收运费。</t>
         </is>
       </c>
     </row>
